--- a/Data/distance_to_nodes.xlsx
+++ b/Data/distance_to_nodes.xlsx
@@ -411,7 +411,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>22.68890426764761</v>
+        <v>32.69564426947834</v>
       </c>
     </row>
     <row r="8">
@@ -2763,7 +2763,7 @@
         <v>299</v>
       </c>
       <c r="B301">
-        <v>10.10816033030017</v>
+        <v>28.31030925084298</v>
       </c>
     </row>
     <row r="302">
@@ -2771,7 +2771,7 @@
         <v>300</v>
       </c>
       <c r="B302">
-        <v>6.820903269753305</v>
+        <v>24.83066983271464</v>
       </c>
     </row>
     <row r="303">
@@ -2787,7 +2787,7 @@
         <v>302</v>
       </c>
       <c r="B304">
-        <v>4.159310683366913</v>
+        <v>23.11140145490911</v>
       </c>
     </row>
     <row r="305">
@@ -2795,7 +2795,7 @@
         <v>303</v>
       </c>
       <c r="B305">
-        <v>13.99994843218879</v>
+        <v>31.47167133919193</v>
       </c>
     </row>
     <row r="306">
@@ -4627,7 +4627,7 @@
         <v>532</v>
       </c>
       <c r="B534">
-        <v>9.944402346374757</v>
+        <v>14.17840247375388</v>
       </c>
     </row>
     <row r="535">
@@ -4851,7 +4851,7 @@
         <v>560</v>
       </c>
       <c r="B562">
-        <v>8.025246123285905</v>
+        <v>16.21505449779126</v>
       </c>
     </row>
     <row r="563">
@@ -4859,7 +4859,7 @@
         <v>561</v>
       </c>
       <c r="B563">
-        <v>0.5113515981456799</v>
+        <v>21.41946394641495</v>
       </c>
     </row>
     <row r="564">
@@ -6283,7 +6283,7 @@
         <v>739</v>
       </c>
       <c r="B741">
-        <v>23.02439115771353</v>
+        <v>26.3580006563763</v>
       </c>
     </row>
     <row r="742">
@@ -6291,7 +6291,7 @@
         <v>740</v>
       </c>
       <c r="B742">
-        <v>22.13615247253638</v>
+        <v>22.28969437733357</v>
       </c>
     </row>
     <row r="743">
@@ -6315,7 +6315,7 @@
         <v>743</v>
       </c>
       <c r="B745">
-        <v>20.45027268858654</v>
+        <v>25.80934536947538</v>
       </c>
     </row>
     <row r="746">
@@ -6331,7 +6331,7 @@
         <v>745</v>
       </c>
       <c r="B747">
-        <v>18.57398663130101</v>
+        <v>23.65828827033505</v>
       </c>
     </row>
     <row r="748">
@@ -6355,7 +6355,7 @@
         <v>748</v>
       </c>
       <c r="B750">
-        <v>18.28207247302696</v>
+        <v>26.52902266127182</v>
       </c>
     </row>
     <row r="751">
@@ -6363,7 +6363,7 @@
         <v>749</v>
       </c>
       <c r="B751">
-        <v>21.45092998779121</v>
+        <v>23.53520707245612</v>
       </c>
     </row>
     <row r="752">
@@ -6379,7 +6379,7 @@
         <v>751</v>
       </c>
       <c r="B753">
-        <v>18.81824062997582</v>
+        <v>22.55517493470134</v>
       </c>
     </row>
     <row r="754">
@@ -6387,7 +6387,7 @@
         <v>752</v>
       </c>
       <c r="B754">
-        <v>13.92791602966524</v>
+        <v>18.89567782986097</v>
       </c>
     </row>
     <row r="755">
@@ -6403,7 +6403,7 @@
         <v>754</v>
       </c>
       <c r="B756">
-        <v>4.869734647962244</v>
+        <v>11.28016467372773</v>
       </c>
     </row>
     <row r="757">
@@ -6419,7 +6419,7 @@
         <v>756</v>
       </c>
       <c r="B758">
-        <v>9.484816209069217</v>
+        <v>13.81078024244813</v>
       </c>
     </row>
     <row r="759">
@@ -6427,7 +6427,7 @@
         <v>757</v>
       </c>
       <c r="B759">
-        <v>18.7669046746945</v>
+        <v>28.35737935024869</v>
       </c>
     </row>
     <row r="760">
@@ -6435,7 +6435,7 @@
         <v>758</v>
       </c>
       <c r="B760">
-        <v>15.49214111796243</v>
+        <v>16.25841323995346</v>
       </c>
     </row>
     <row r="761">
@@ -7099,7 +7099,7 @@
         <v>841</v>
       </c>
       <c r="B843">
-        <v>21.42181156028578</v>
+        <v>19.65390851242243</v>
       </c>
     </row>
     <row r="844">
@@ -7107,7 +7107,7 @@
         <v>842</v>
       </c>
       <c r="B844">
-        <v>22.49522263623879</v>
+        <v>21.38233355225105</v>
       </c>
     </row>
     <row r="845">
@@ -7115,7 +7115,7 @@
         <v>843</v>
       </c>
       <c r="B845">
-        <v>16.19161085190039</v>
+        <v>13.8605616975647</v>
       </c>
     </row>
     <row r="846">
@@ -7123,7 +7123,7 @@
         <v>844</v>
       </c>
       <c r="B846">
-        <v>20.9797932727014</v>
+        <v>18.69497252898393</v>
       </c>
     </row>
     <row r="847">
@@ -7131,7 +7131,7 @@
         <v>845</v>
       </c>
       <c r="B847">
-        <v>16.72536110107141</v>
+        <v>14.80905044784205</v>
       </c>
     </row>
     <row r="848">
@@ -7139,7 +7139,7 @@
         <v>846</v>
       </c>
       <c r="B848">
-        <v>19.50172462641531</v>
+        <v>18.39870558878141</v>
       </c>
     </row>
     <row r="849">
@@ -7155,7 +7155,7 @@
         <v>848</v>
       </c>
       <c r="B850">
-        <v>24.16635132296783</v>
+        <v>21.9705101648932</v>
       </c>
     </row>
     <row r="851">
@@ -7163,7 +7163,7 @@
         <v>849</v>
       </c>
       <c r="B851">
-        <v>19.49520767934272</v>
+        <v>16.90481363442589</v>
       </c>
     </row>
     <row r="852">
@@ -7171,7 +7171,7 @@
         <v>850</v>
       </c>
       <c r="B852">
-        <v>23.65685581179383</v>
+        <v>21.68222116567546</v>
       </c>
     </row>
     <row r="853">
@@ -7187,7 +7187,7 @@
         <v>852</v>
       </c>
       <c r="B854">
-        <v>16.62252273937216</v>
+        <v>15.24053375330743</v>
       </c>
     </row>
     <row r="855">
@@ -7299,7 +7299,7 @@
         <v>866</v>
       </c>
       <c r="B868">
-        <v>6.801876198379063</v>
+        <v>6.306982972332919</v>
       </c>
     </row>
     <row r="869">
@@ -7307,7 +7307,7 @@
         <v>867</v>
       </c>
       <c r="B869">
-        <v>8.900894857005918</v>
+        <v>8.93959382185113</v>
       </c>
     </row>
     <row r="870">
@@ -7323,7 +7323,7 @@
         <v>869</v>
       </c>
       <c r="B871">
-        <v>11.96872854148653</v>
+        <v>10.91660469586549</v>
       </c>
     </row>
     <row r="872">
@@ -7347,7 +7347,7 @@
         <v>872</v>
       </c>
       <c r="B874">
-        <v>18.27377477470923</v>
+        <v>18.6967397880025</v>
       </c>
     </row>
     <row r="875">
@@ -7363,7 +7363,7 @@
         <v>874</v>
       </c>
       <c r="B876">
-        <v>17.87428310803395</v>
+        <v>17.3803224755321</v>
       </c>
     </row>
     <row r="877">
@@ -7371,7 +7371,7 @@
         <v>875</v>
       </c>
       <c r="B877">
-        <v>14.70861967983075</v>
+        <v>14.11035630506033</v>
       </c>
     </row>
     <row r="878">
@@ -7379,7 +7379,7 @@
         <v>876</v>
       </c>
       <c r="B878">
-        <v>14.56119732156985</v>
+        <v>14.55254208396978</v>
       </c>
     </row>
     <row r="879">
@@ -7403,7 +7403,7 @@
         <v>879</v>
       </c>
       <c r="B881">
-        <v>11.0455365572774</v>
+        <v>10.78900252384516</v>
       </c>
     </row>
     <row r="882">
@@ -7827,7 +7827,7 @@
         <v>932</v>
       </c>
       <c r="B934">
-        <v>14.80921083333351</v>
+        <v>15.49414830618528</v>
       </c>
     </row>
     <row r="935">
@@ -7851,7 +7851,7 @@
         <v>935</v>
       </c>
       <c r="B937">
-        <v>13.41104083002249</v>
+        <v>14.1694078138738</v>
       </c>
     </row>
     <row r="938">
@@ -7867,7 +7867,7 @@
         <v>937</v>
       </c>
       <c r="B939">
-        <v>6.479186244217921</v>
+        <v>7.593248007981491</v>
       </c>
     </row>
     <row r="940">
@@ -7907,7 +7907,7 @@
         <v>942</v>
       </c>
       <c r="B944">
-        <v>9.316722992772174</v>
+        <v>11.03624346950976</v>
       </c>
     </row>
     <row r="945">
@@ -7915,7 +7915,7 @@
         <v>943</v>
       </c>
       <c r="B945">
-        <v>12.42437791206936</v>
+        <v>13.20512845698603</v>
       </c>
     </row>
     <row r="946">
@@ -8099,7 +8099,7 @@
         <v>966</v>
       </c>
       <c r="B968">
-        <v>11.85630293528173</v>
+        <v>8.920214792607071</v>
       </c>
     </row>
     <row r="969">
@@ -8107,7 +8107,7 @@
         <v>967</v>
       </c>
       <c r="B969">
-        <v>14.72806652491029</v>
+        <v>11.82964498135253</v>
       </c>
     </row>
     <row r="970">
@@ -8115,7 +8115,7 @@
         <v>968</v>
       </c>
       <c r="B970">
-        <v>16.65318338247413</v>
+        <v>14.12211206864431</v>
       </c>
     </row>
     <row r="971">
@@ -8123,7 +8123,7 @@
         <v>969</v>
       </c>
       <c r="B971">
-        <v>4.329742754778716</v>
+        <v>1.714410359024305</v>
       </c>
     </row>
     <row r="972">
@@ -8131,7 +8131,7 @@
         <v>970</v>
       </c>
       <c r="B972">
-        <v>12.06107822984307</v>
+        <v>9.985674461536117</v>
       </c>
     </row>
     <row r="973">
@@ -8139,7 +8139,7 @@
         <v>971</v>
       </c>
       <c r="B973">
-        <v>12.17875737154927</v>
+        <v>9.511204507116107</v>
       </c>
     </row>
     <row r="974">
@@ -8147,7 +8147,7 @@
         <v>972</v>
       </c>
       <c r="B974">
-        <v>12.53525088308245</v>
+        <v>9.812459017599531</v>
       </c>
     </row>
     <row r="975">
@@ -8155,7 +8155,7 @@
         <v>973</v>
       </c>
       <c r="B975">
-        <v>9.936982722872296</v>
+        <v>7.16712873994878</v>
       </c>
     </row>
     <row r="976">
@@ -8163,7 +8163,7 @@
         <v>974</v>
       </c>
       <c r="B976">
-        <v>13.10914744244024</v>
+        <v>10.8776215075781</v>
       </c>
     </row>
     <row r="977">
@@ -8171,7 +8171,7 @@
         <v>975</v>
       </c>
       <c r="B977">
-        <v>6.57723881833802</v>
+        <v>4.232436656350789</v>
       </c>
     </row>
     <row r="978">
@@ -8179,7 +8179,7 @@
         <v>976</v>
       </c>
       <c r="B978">
-        <v>17.35910146690644</v>
+        <v>14.51391367471693</v>
       </c>
     </row>
     <row r="979">
@@ -8187,7 +8187,7 @@
         <v>977</v>
       </c>
       <c r="B979">
-        <v>8.176936501283164</v>
+        <v>5.509956006905899</v>
       </c>
     </row>
     <row r="980">
@@ -8195,7 +8195,7 @@
         <v>978</v>
       </c>
       <c r="B980">
-        <v>8.420116806889435</v>
+        <v>6.602531664937675</v>
       </c>
     </row>
     <row r="981">
@@ -8203,7 +8203,7 @@
         <v>979</v>
       </c>
       <c r="B981">
-        <v>16.49296341513305</v>
+        <v>25.52254620683486</v>
       </c>
     </row>
     <row r="982">
@@ -8211,7 +8211,7 @@
         <v>980</v>
       </c>
       <c r="B982">
-        <v>12.78901487498386</v>
+        <v>22.09045143432118</v>
       </c>
     </row>
     <row r="983">
@@ -8219,7 +8219,7 @@
         <v>981</v>
       </c>
       <c r="B983">
-        <v>9.385656593927763</v>
+        <v>20.0478210117097</v>
       </c>
     </row>
     <row r="984">
@@ -8227,7 +8227,7 @@
         <v>982</v>
       </c>
       <c r="B984">
-        <v>10.97771344252947</v>
+        <v>18.12300782455958</v>
       </c>
     </row>
     <row r="985">
@@ -8235,7 +8235,7 @@
         <v>983</v>
       </c>
       <c r="B985">
-        <v>11.35750342393446</v>
+        <v>22.58286726743913</v>
       </c>
     </row>
     <row r="986">
@@ -8243,7 +8243,7 @@
         <v>984</v>
       </c>
       <c r="B986">
-        <v>8.04372111219508</v>
+        <v>17.50685840717249</v>
       </c>
     </row>
     <row r="987">
@@ -8251,7 +8251,7 @@
         <v>985</v>
       </c>
       <c r="B987">
-        <v>17.36591208031297</v>
+        <v>23.57932037443232</v>
       </c>
     </row>
     <row r="988">
@@ -8259,7 +8259,7 @@
         <v>986</v>
       </c>
       <c r="B988">
-        <v>21.46841331358653</v>
+        <v>28.66150841427597</v>
       </c>
     </row>
     <row r="989">
@@ -8267,7 +8267,7 @@
         <v>987</v>
       </c>
       <c r="B989">
-        <v>10.81684670267225</v>
+        <v>21.94404804210425</v>
       </c>
     </row>
     <row r="990">
@@ -8347,7 +8347,7 @@
         <v>997</v>
       </c>
       <c r="B999">
-        <v>10.95785424937756</v>
+        <v>12.57761939936718</v>
       </c>
     </row>
     <row r="1000">
@@ -8363,7 +8363,7 @@
         <v>999</v>
       </c>
       <c r="B1001">
-        <v>8.336451220527774</v>
+        <v>14.59799581025459</v>
       </c>
     </row>
     <row r="1002">
@@ -8379,7 +8379,7 @@
         <v>1001</v>
       </c>
       <c r="B1003">
-        <v>11.92766163079851</v>
+        <v>14.60382992552079</v>
       </c>
     </row>
     <row r="1004">
@@ -8387,7 +8387,7 @@
         <v>1002</v>
       </c>
       <c r="B1004">
-        <v>10.5246677954652</v>
+        <v>12.83429868554952</v>
       </c>
     </row>
     <row r="1005">
@@ -8395,7 +8395,7 @@
         <v>1003</v>
       </c>
       <c r="B1005">
-        <v>8.823289604887609</v>
+        <v>11.30404102117589</v>
       </c>
     </row>
     <row r="1006">
@@ -8403,7 +8403,7 @@
         <v>1004</v>
       </c>
       <c r="B1006">
-        <v>8.845700007249018</v>
+        <v>11.7685686957084</v>
       </c>
     </row>
     <row r="1007">
@@ -8419,7 +8419,7 @@
         <v>1006</v>
       </c>
       <c r="B1008">
-        <v>6.736585075311883</v>
+        <v>17.77247131420545</v>
       </c>
     </row>
     <row r="1009">
@@ -8427,7 +8427,7 @@
         <v>1007</v>
       </c>
       <c r="B1009">
-        <v>4.774375315110579</v>
+        <v>15.18605937058122</v>
       </c>
     </row>
     <row r="1010">
@@ -8443,7 +8443,7 @@
         <v>1009</v>
       </c>
       <c r="B1011">
-        <v>0.7342951183532037</v>
+        <v>11.92156369626311</v>
       </c>
     </row>
     <row r="1012">
@@ -8451,7 +8451,7 @@
         <v>1010</v>
       </c>
       <c r="B1012">
-        <v>1.005425233267728</v>
+        <v>10.78751254477635</v>
       </c>
     </row>
     <row r="1013">
@@ -8467,7 +8467,7 @@
         <v>1012</v>
       </c>
       <c r="B1014">
-        <v>7.338419672492251</v>
+        <v>18.52452856849868</v>
       </c>
     </row>
     <row r="1015">
@@ -8491,7 +8491,7 @@
         <v>1015</v>
       </c>
       <c r="B1017">
-        <v>5.032737652332683</v>
+        <v>10.95476368544092</v>
       </c>
     </row>
     <row r="1018">
@@ -8507,7 +8507,7 @@
         <v>1017</v>
       </c>
       <c r="B1019">
-        <v>21.77838752035956</v>
+        <v>22.8850024213061</v>
       </c>
     </row>
     <row r="1020">
@@ -8515,7 +8515,7 @@
         <v>1018</v>
       </c>
       <c r="B1020">
-        <v>18.87627066174108</v>
+        <v>20.3678326598375</v>
       </c>
     </row>
     <row r="1021">
@@ -8523,7 +8523,7 @@
         <v>1019</v>
       </c>
       <c r="B1021">
-        <v>21.86754100069239</v>
+        <v>23.56948507444276</v>
       </c>
     </row>
     <row r="1022">
@@ -8531,7 +8531,7 @@
         <v>1020</v>
       </c>
       <c r="B1022">
-        <v>5.895271467174473</v>
+        <v>8.727620073462889</v>
       </c>
     </row>
     <row r="1023">
@@ -8539,7 +8539,7 @@
         <v>1021</v>
       </c>
       <c r="B1023">
-        <v>4.926288307002339</v>
+        <v>6.7385465457903</v>
       </c>
     </row>
     <row r="1024">
@@ -8547,7 +8547,7 @@
         <v>1022</v>
       </c>
       <c r="B1024">
-        <v>8.315523484891372</v>
+        <v>10.43366744837717</v>
       </c>
     </row>
     <row r="1025">
@@ -8555,7 +8555,7 @@
         <v>1023</v>
       </c>
       <c r="B1025">
-        <v>5.349276700650416</v>
+        <v>8.118944230188216</v>
       </c>
     </row>
     <row r="1026">
@@ -8563,7 +8563,7 @@
         <v>1024</v>
       </c>
       <c r="B1026">
-        <v>7.111332213750659</v>
+        <v>9.508648129013466</v>
       </c>
     </row>
     <row r="1027">
@@ -8571,7 +8571,7 @@
         <v>1025</v>
       </c>
       <c r="B1027">
-        <v>22.22504355744513</v>
+        <v>21.64950372652624</v>
       </c>
     </row>
     <row r="1028">
@@ -8579,7 +8579,7 @@
         <v>1026</v>
       </c>
       <c r="B1028">
-        <v>7.624815221760368</v>
+        <v>7.100262537981658</v>
       </c>
     </row>
     <row r="1029">
@@ -8595,7 +8595,7 @@
         <v>1028</v>
       </c>
       <c r="B1030">
-        <v>22.66979779760182</v>
+        <v>21.19002101561528</v>
       </c>
     </row>
     <row r="1031">
@@ -8603,7 +8603,7 @@
         <v>1029</v>
       </c>
       <c r="B1031">
-        <v>12.14410868371082</v>
+        <v>10.89683881179044</v>
       </c>
     </row>
     <row r="1032">
@@ -8611,7 +8611,7 @@
         <v>1030</v>
       </c>
       <c r="B1032">
-        <v>3.829650916653252</v>
+        <v>2.699337278754647</v>
       </c>
     </row>
     <row r="1033">
@@ -8619,7 +8619,7 @@
         <v>1031</v>
       </c>
       <c r="B1033">
-        <v>19.69633273063405</v>
+        <v>17.74704956858763</v>
       </c>
     </row>
     <row r="1034">
@@ -8627,7 +8627,7 @@
         <v>1032</v>
       </c>
       <c r="B1034">
-        <v>17.98165975846372</v>
+        <v>16.55203774469037</v>
       </c>
     </row>
     <row r="1035">
@@ -8643,7 +8643,7 @@
         <v>1034</v>
       </c>
       <c r="B1036">
-        <v>13.81844086345078</v>
+        <v>12.10016086527797</v>
       </c>
     </row>
     <row r="1037">
@@ -8659,7 +8659,7 @@
         <v>1036</v>
       </c>
       <c r="B1038">
-        <v>16.72578789112604</v>
+        <v>14.41183207715983</v>
       </c>
     </row>
     <row r="1039">
@@ -8667,7 +8667,7 @@
         <v>1037</v>
       </c>
       <c r="B1039">
-        <v>18.22407726798037</v>
+        <v>16.52803447182866</v>
       </c>
     </row>
     <row r="1040">
@@ -8675,7 +8675,7 @@
         <v>1038</v>
       </c>
       <c r="B1040">
-        <v>18.83164021078667</v>
+        <v>16.60646821359574</v>
       </c>
     </row>
     <row r="1041">
@@ -8683,7 +8683,7 @@
         <v>1039</v>
       </c>
       <c r="B1041">
-        <v>20.15032488589116</v>
+        <v>20.16734568436619</v>
       </c>
     </row>
     <row r="1042">
@@ -8691,7 +8691,7 @@
         <v>1040</v>
       </c>
       <c r="B1042">
-        <v>16.95529327165244</v>
+        <v>15.77590722418053</v>
       </c>
     </row>
     <row r="1043">
@@ -8699,7 +8699,7 @@
         <v>1041</v>
       </c>
       <c r="B1043">
-        <v>25.76042506694605</v>
+        <v>26.00889933028632</v>
       </c>
     </row>
     <row r="1044">
@@ -8707,7 +8707,7 @@
         <v>1042</v>
       </c>
       <c r="B1044">
-        <v>19.89665323387234</v>
+        <v>18.88729517883474</v>
       </c>
     </row>
     <row r="1045">
@@ -8715,7 +8715,7 @@
         <v>1043</v>
       </c>
       <c r="B1045">
-        <v>9.014944674336999</v>
+        <v>7.091951068546098</v>
       </c>
     </row>
     <row r="1046">
@@ -8755,7 +8755,7 @@
         <v>1048</v>
       </c>
       <c r="B1050">
-        <v>17.8817238953763</v>
+        <v>17.34808611312392</v>
       </c>
     </row>
     <row r="1051">
@@ -9147,7 +9147,7 @@
         <v>1097</v>
       </c>
       <c r="B1099">
-        <v>16.22498622328425</v>
+        <v>13.30534833739332</v>
       </c>
     </row>
     <row r="1100">
@@ -9155,7 +9155,7 @@
         <v>1098</v>
       </c>
       <c r="B1100">
-        <v>18.16659459177931</v>
+        <v>16.59293432232049</v>
       </c>
     </row>
     <row r="1101">
@@ -9171,7 +9171,7 @@
         <v>1100</v>
       </c>
       <c r="B1102">
-        <v>15.65848541488306</v>
+        <v>12.91066863426261</v>
       </c>
     </row>
     <row r="1103">
@@ -9187,7 +9187,7 @@
         <v>1102</v>
       </c>
       <c r="B1104">
-        <v>19.16414331284514</v>
+        <v>16.33895280646302</v>
       </c>
     </row>
     <row r="1105">
@@ -9283,7 +9283,7 @@
         <v>1114</v>
       </c>
       <c r="B1116">
-        <v>23.250410214744</v>
+        <v>21.58432581591429</v>
       </c>
     </row>
     <row r="1117">
@@ -9315,7 +9315,7 @@
         <v>1118</v>
       </c>
       <c r="B1120">
-        <v>26.29896998594824</v>
+        <v>24.45335495349909</v>
       </c>
     </row>
     <row r="1121">
@@ -9331,7 +9331,7 @@
         <v>1120</v>
       </c>
       <c r="B1122">
-        <v>25.26335813791615</v>
+        <v>25.10865721582872</v>
       </c>
     </row>
     <row r="1123">
@@ -12531,7 +12531,7 @@
         <v>1520</v>
       </c>
       <c r="B1522">
-        <v>31.28104069113134</v>
+        <v>32.2148932777988</v>
       </c>
     </row>
     <row r="1523">
@@ -12547,7 +12547,7 @@
         <v>1522</v>
       </c>
       <c r="B1524">
-        <v>25.22551916038001</v>
+        <v>26.4841389279218</v>
       </c>
     </row>
     <row r="1525">
@@ -12723,7 +12723,7 @@
         <v>1544</v>
       </c>
       <c r="B1546">
-        <v>14.32195099841462</v>
+        <v>24.27405235466027</v>
       </c>
     </row>
     <row r="1547">
@@ -12731,7 +12731,7 @@
         <v>1545</v>
       </c>
       <c r="B1547">
-        <v>9.090132319049887</v>
+        <v>18.26172902742485</v>
       </c>
     </row>
     <row r="1548">
@@ -12955,7 +12955,7 @@
         <v>1573</v>
       </c>
       <c r="B1575">
-        <v>3.754579480593483</v>
+        <v>5.171387257630506</v>
       </c>
     </row>
     <row r="1576">
@@ -13179,7 +13179,7 @@
         <v>1601</v>
       </c>
       <c r="B1603">
-        <v>1.664285240316347</v>
+        <v>19.60303123231912</v>
       </c>
     </row>
     <row r="1604">
@@ -13507,7 +13507,7 @@
         <v>1642</v>
       </c>
       <c r="B1644">
-        <v>2.028806557049571</v>
+        <v>4.963108320108936</v>
       </c>
     </row>
     <row r="1645">
@@ -13515,7 +13515,7 @@
         <v>1643</v>
       </c>
       <c r="B1645">
-        <v>0.833576887307609</v>
+        <v>2.594152426327075</v>
       </c>
     </row>
     <row r="1646">
@@ -13579,7 +13579,7 @@
         <v>1651</v>
       </c>
       <c r="B1653">
-        <v>17.16944212786941</v>
+        <v>28.45283509252831</v>
       </c>
     </row>
     <row r="1654">
@@ -13859,7 +13859,7 @@
         <v>1686</v>
       </c>
       <c r="B1688">
-        <v>15.72207059893756</v>
+        <v>19.21885102017499</v>
       </c>
     </row>
     <row r="1689">
@@ -13867,7 +13867,7 @@
         <v>1687</v>
       </c>
       <c r="B1689">
-        <v>15.62023236319789</v>
+        <v>16.82963245067203</v>
       </c>
     </row>
     <row r="1690">
@@ -13875,7 +13875,7 @@
         <v>1688</v>
       </c>
       <c r="B1690">
-        <v>8.213200592680051</v>
+        <v>9.188856624135081</v>
       </c>
     </row>
     <row r="1691">
@@ -13883,7 +13883,7 @@
         <v>1689</v>
       </c>
       <c r="B1691">
-        <v>12.38057977901964</v>
+        <v>14.02844543013261</v>
       </c>
     </row>
     <row r="1692">
@@ -13891,7 +13891,7 @@
         <v>1690</v>
       </c>
       <c r="B1692">
-        <v>17.2757676515808</v>
+        <v>16.82875973704438</v>
       </c>
     </row>
     <row r="1693">
@@ -13899,7 +13899,7 @@
         <v>1691</v>
       </c>
       <c r="B1693">
-        <v>13.32526951047298</v>
+        <v>15.40550577448183</v>
       </c>
     </row>
     <row r="1694">
@@ -13907,7 +13907,7 @@
         <v>1692</v>
       </c>
       <c r="B1694">
-        <v>18.65574960613958</v>
+        <v>19.28709925683625</v>
       </c>
     </row>
     <row r="1695">
@@ -13915,7 +13915,7 @@
         <v>1693</v>
       </c>
       <c r="B1695">
-        <v>10.51959486270761</v>
+        <v>12.02524259887938</v>
       </c>
     </row>
     <row r="1696">
@@ -13923,7 +13923,7 @@
         <v>1694</v>
       </c>
       <c r="B1696">
-        <v>12.01440772142921</v>
+        <v>11.75283238724364</v>
       </c>
     </row>
     <row r="1697">
@@ -14147,7 +14147,7 @@
         <v>1722</v>
       </c>
       <c r="B1724">
-        <v>7.030324408798631</v>
+        <v>21.86611005785238</v>
       </c>
     </row>
     <row r="1725">
@@ -14155,7 +14155,7 @@
         <v>1723</v>
       </c>
       <c r="B1725">
-        <v>11.0966670556566</v>
+        <v>17.67423265702337</v>
       </c>
     </row>
     <row r="1726">
@@ -14747,7 +14747,7 @@
         <v>1797</v>
       </c>
       <c r="B1799">
-        <v>6.861527223957914</v>
+        <v>12.6660519952372</v>
       </c>
     </row>
     <row r="1800">
@@ -14755,7 +14755,7 @@
         <v>1798</v>
       </c>
       <c r="B1800">
-        <v>0.7425268006477894</v>
+        <v>18.99824692819093</v>
       </c>
     </row>
     <row r="1801">
@@ -15099,7 +15099,7 @@
         <v>1841</v>
       </c>
       <c r="B1843">
-        <v>5.801037863469992</v>
+        <v>17.60754497784202</v>
       </c>
     </row>
     <row r="1844">
@@ -15107,7 +15107,7 @@
         <v>1842</v>
       </c>
       <c r="B1844">
-        <v>4.014055798917167</v>
+        <v>25.11308221652199</v>
       </c>
     </row>
     <row r="1845">
@@ -15115,7 +15115,7 @@
         <v>1843</v>
       </c>
       <c r="B1845">
-        <v>4.136660131267364</v>
+        <v>22.69671866769873</v>
       </c>
     </row>
     <row r="1846">

--- a/Data/distance_to_nodes.xlsx
+++ b/Data/distance_to_nodes.xlsx
@@ -435,7 +435,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>10.23067103786667</v>
+        <v>11.54983401634882</v>
       </c>
     </row>
     <row r="11">
@@ -5723,7 +5723,7 @@
         <v>669</v>
       </c>
       <c r="B671">
-        <v>7.169759706137335</v>
+        <v>11.10864464596096</v>
       </c>
     </row>
     <row r="672">
@@ -5739,7 +5739,7 @@
         <v>671</v>
       </c>
       <c r="B673">
-        <v>12.6608281338653</v>
+        <v>14.81992176338797</v>
       </c>
     </row>
     <row r="674">
@@ -5755,7 +5755,7 @@
         <v>673</v>
       </c>
       <c r="B675">
-        <v>7.665865751589187</v>
+        <v>10.81494511769893</v>
       </c>
     </row>
     <row r="676">
@@ -5771,7 +5771,7 @@
         <v>675</v>
       </c>
       <c r="B677">
-        <v>9.004755568546045</v>
+        <v>12.1121912600838</v>
       </c>
     </row>
     <row r="678">
@@ -5779,7 +5779,7 @@
         <v>676</v>
       </c>
       <c r="B678">
-        <v>10.8242699340075</v>
+        <v>14.11765317044713</v>
       </c>
     </row>
     <row r="679">
@@ -5819,7 +5819,7 @@
         <v>681</v>
       </c>
       <c r="B683">
-        <v>10.79491606155203</v>
+        <v>11.78543575293354</v>
       </c>
     </row>
     <row r="684">
@@ -5827,7 +5827,7 @@
         <v>682</v>
       </c>
       <c r="B684">
-        <v>4.412963922663391</v>
+        <v>8.144725093370878</v>
       </c>
     </row>
     <row r="685">
@@ -5835,7 +5835,7 @@
         <v>683</v>
       </c>
       <c r="B685">
-        <v>9.854762446749598</v>
+        <v>12.55858441985141</v>
       </c>
     </row>
     <row r="686">
@@ -5843,7 +5843,7 @@
         <v>684</v>
       </c>
       <c r="B686">
-        <v>4.598105152763946</v>
+        <v>7.321101686025758</v>
       </c>
     </row>
     <row r="687">
@@ -5851,7 +5851,7 @@
         <v>685</v>
       </c>
       <c r="B687">
-        <v>7.635327254878974</v>
+        <v>9.804473046266018</v>
       </c>
     </row>
     <row r="688">
@@ -5859,7 +5859,7 @@
         <v>686</v>
       </c>
       <c r="B688">
-        <v>16.48344853640133</v>
+        <v>16.48927030351638</v>
       </c>
     </row>
     <row r="689">
@@ -5867,7 +5867,7 @@
         <v>687</v>
       </c>
       <c r="B689">
-        <v>18.8782730987104</v>
+        <v>19.20051966834479</v>
       </c>
     </row>
     <row r="690">
@@ -5875,7 +5875,7 @@
         <v>688</v>
       </c>
       <c r="B690">
-        <v>4.358549395868627</v>
+        <v>4.772453666470098</v>
       </c>
     </row>
     <row r="691">
@@ -5883,7 +5883,7 @@
         <v>689</v>
       </c>
       <c r="B691">
-        <v>7.414197788012176</v>
+        <v>5.745534633184374</v>
       </c>
     </row>
     <row r="692">
@@ -5891,7 +5891,7 @@
         <v>690</v>
       </c>
       <c r="B692">
-        <v>9.445513526675198</v>
+        <v>10.63070557072331</v>
       </c>
     </row>
     <row r="693">
@@ -5899,7 +5899,7 @@
         <v>691</v>
       </c>
       <c r="B693">
-        <v>0.6570976947526809</v>
+        <v>4.482208435682622</v>
       </c>
     </row>
     <row r="694">
@@ -5907,7 +5907,7 @@
         <v>692</v>
       </c>
       <c r="B694">
-        <v>11.63821813048884</v>
+        <v>12.80800619263842</v>
       </c>
     </row>
     <row r="695">
@@ -5915,7 +5915,7 @@
         <v>693</v>
       </c>
       <c r="B695">
-        <v>14.54172132841914</v>
+        <v>15.21015208826595</v>
       </c>
     </row>
     <row r="696">
@@ -5923,7 +5923,7 @@
         <v>694</v>
       </c>
       <c r="B696">
-        <v>14.89746048274498</v>
+        <v>16.06612292096207</v>
       </c>
     </row>
     <row r="697">
@@ -5931,7 +5931,7 @@
         <v>695</v>
       </c>
       <c r="B697">
-        <v>9.146627617427178</v>
+        <v>8.938187965311542</v>
       </c>
     </row>
     <row r="698">
@@ -5939,7 +5939,7 @@
         <v>696</v>
       </c>
       <c r="B698">
-        <v>10.92423540190597</v>
+        <v>8.982384227008918</v>
       </c>
     </row>
     <row r="699">
@@ -5947,7 +5947,7 @@
         <v>697</v>
       </c>
       <c r="B699">
-        <v>15.12308954941143</v>
+        <v>13.13818129567564</v>
       </c>
     </row>
     <row r="700">
@@ -5971,7 +5971,7 @@
         <v>700</v>
       </c>
       <c r="B702">
-        <v>24.52905358911021</v>
+        <v>25.06240455691745</v>
       </c>
     </row>
     <row r="703">
@@ -6195,7 +6195,7 @@
         <v>728</v>
       </c>
       <c r="B730">
-        <v>24.37669962128605</v>
+        <v>24.29058454274987</v>
       </c>
     </row>
     <row r="731">
@@ -6955,7 +6955,7 @@
         <v>823</v>
       </c>
       <c r="B825">
-        <v>7.983807304076199</v>
+        <v>5.121266566198885</v>
       </c>
     </row>
     <row r="826">
@@ -6963,7 +6963,7 @@
         <v>824</v>
       </c>
       <c r="B826">
-        <v>12.6936071560663</v>
+        <v>8.791985178004104</v>
       </c>
     </row>
     <row r="827">
@@ -6971,7 +6971,7 @@
         <v>825</v>
       </c>
       <c r="B827">
-        <v>12.65045280106634</v>
+        <v>9.166075079656563</v>
       </c>
     </row>
     <row r="828">
@@ -6979,7 +6979,7 @@
         <v>826</v>
       </c>
       <c r="B828">
-        <v>10.06344511801272</v>
+        <v>7.33676973036225</v>
       </c>
     </row>
     <row r="829">
@@ -6987,7 +6987,7 @@
         <v>827</v>
       </c>
       <c r="B829">
-        <v>7.882092364183232</v>
+        <v>6.966845059647171</v>
       </c>
     </row>
     <row r="830">
@@ -7691,7 +7691,7 @@
         <v>915</v>
       </c>
       <c r="B917">
-        <v>13.96312784505244</v>
+        <v>10.13906715761937</v>
       </c>
     </row>
     <row r="918">
@@ -7723,7 +7723,7 @@
         <v>919</v>
       </c>
       <c r="B921">
-        <v>16.16827045473892</v>
+        <v>12.6441948171023</v>
       </c>
     </row>
     <row r="922">
@@ -7739,7 +7739,7 @@
         <v>921</v>
       </c>
       <c r="B923">
-        <v>14.61716757563276</v>
+        <v>14.61583081285974</v>
       </c>
     </row>
     <row r="924">
@@ -7763,7 +7763,7 @@
         <v>924</v>
       </c>
       <c r="B926">
-        <v>15.41689561481942</v>
+        <v>13.96189734708826</v>
       </c>
     </row>
     <row r="927">
@@ -7779,7 +7779,7 @@
         <v>926</v>
       </c>
       <c r="B928">
-        <v>13.13931783597519</v>
+        <v>10.28337323986755</v>
       </c>
     </row>
     <row r="929">
@@ -7787,7 +7787,7 @@
         <v>927</v>
       </c>
       <c r="B929">
-        <v>12.12323791511188</v>
+        <v>11.4831807530126</v>
       </c>
     </row>
     <row r="930">
@@ -7795,7 +7795,7 @@
         <v>928</v>
       </c>
       <c r="B930">
-        <v>17.92346636344088</v>
+        <v>16.57202757054716</v>
       </c>
     </row>
     <row r="931">
@@ -7803,7 +7803,7 @@
         <v>929</v>
       </c>
       <c r="B931">
-        <v>13.2045279464996</v>
+        <v>11.38175674715957</v>
       </c>
     </row>
     <row r="932">
@@ -12699,7 +12699,7 @@
         <v>1541</v>
       </c>
       <c r="B1543">
-        <v>6.009357908404844</v>
+        <v>2.404824156144181</v>
       </c>
     </row>
     <row r="1544">
@@ -12707,7 +12707,7 @@
         <v>1542</v>
       </c>
       <c r="B1544">
-        <v>4.395000357939532</v>
+        <v>3.445193193983564</v>
       </c>
     </row>
     <row r="1545">
@@ -13675,7 +13675,7 @@
         <v>1663</v>
       </c>
       <c r="B1665">
-        <v>13.6467438450352</v>
+        <v>12.4964767260809</v>
       </c>
     </row>
     <row r="1666">
@@ -13683,7 +13683,7 @@
         <v>1664</v>
       </c>
       <c r="B1666">
-        <v>13.25763680365672</v>
+        <v>12.99173626714352</v>
       </c>
     </row>
     <row r="1667">
@@ -13691,7 +13691,7 @@
         <v>1665</v>
       </c>
       <c r="B1667">
-        <v>16.48301317626168</v>
+        <v>15.21236958031177</v>
       </c>
     </row>
     <row r="1668">
@@ -13755,7 +13755,7 @@
         <v>1673</v>
       </c>
       <c r="B1675">
-        <v>9.443089075137932</v>
+        <v>5.626591533553919</v>
       </c>
     </row>
     <row r="1676">
@@ -13763,7 +13763,7 @@
         <v>1674</v>
       </c>
       <c r="B1676">
-        <v>7.765696816126778</v>
+        <v>3.998091017946646</v>
       </c>
     </row>
     <row r="1677">

--- a/Data/distance_to_nodes.xlsx
+++ b/Data/distance_to_nodes.xlsx
@@ -7099,7 +7099,7 @@
         <v>841</v>
       </c>
       <c r="B843">
-        <v>19.65390851242243</v>
+        <v>21.42181156028578</v>
       </c>
     </row>
     <row r="844">
@@ -7107,7 +7107,7 @@
         <v>842</v>
       </c>
       <c r="B844">
-        <v>21.38233355225105</v>
+        <v>22.49522263623879</v>
       </c>
     </row>
     <row r="845">
@@ -7115,7 +7115,7 @@
         <v>843</v>
       </c>
       <c r="B845">
-        <v>13.8605616975647</v>
+        <v>16.19161085190039</v>
       </c>
     </row>
     <row r="846">
@@ -7123,7 +7123,7 @@
         <v>844</v>
       </c>
       <c r="B846">
-        <v>18.69497252898393</v>
+        <v>20.9797932727014</v>
       </c>
     </row>
     <row r="847">
@@ -7131,7 +7131,7 @@
         <v>845</v>
       </c>
       <c r="B847">
-        <v>14.80905044784205</v>
+        <v>16.72536110107141</v>
       </c>
     </row>
     <row r="848">
@@ -7139,7 +7139,7 @@
         <v>846</v>
       </c>
       <c r="B848">
-        <v>18.39870558878141</v>
+        <v>19.50172462641531</v>
       </c>
     </row>
     <row r="849">
@@ -7155,7 +7155,7 @@
         <v>848</v>
       </c>
       <c r="B850">
-        <v>21.9705101648932</v>
+        <v>24.16635132296783</v>
       </c>
     </row>
     <row r="851">
@@ -7163,7 +7163,7 @@
         <v>849</v>
       </c>
       <c r="B851">
-        <v>16.90481363442589</v>
+        <v>19.49520767934272</v>
       </c>
     </row>
     <row r="852">
@@ -7171,7 +7171,7 @@
         <v>850</v>
       </c>
       <c r="B852">
-        <v>21.68222116567546</v>
+        <v>23.65685581179383</v>
       </c>
     </row>
     <row r="853">
@@ -7187,7 +7187,7 @@
         <v>852</v>
       </c>
       <c r="B854">
-        <v>15.24053375330743</v>
+        <v>16.62252273937216</v>
       </c>
     </row>
     <row r="855">
@@ -7299,7 +7299,7 @@
         <v>866</v>
       </c>
       <c r="B868">
-        <v>6.306982972332919</v>
+        <v>6.801876198379063</v>
       </c>
     </row>
     <row r="869">
@@ -7307,7 +7307,7 @@
         <v>867</v>
       </c>
       <c r="B869">
-        <v>8.93959382185113</v>
+        <v>8.900894857005918</v>
       </c>
     </row>
     <row r="870">
@@ -7323,7 +7323,7 @@
         <v>869</v>
       </c>
       <c r="B871">
-        <v>10.91660469586549</v>
+        <v>11.96872854148653</v>
       </c>
     </row>
     <row r="872">
@@ -7347,7 +7347,7 @@
         <v>872</v>
       </c>
       <c r="B874">
-        <v>18.6967397880025</v>
+        <v>18.27377477470923</v>
       </c>
     </row>
     <row r="875">
@@ -7363,7 +7363,7 @@
         <v>874</v>
       </c>
       <c r="B876">
-        <v>17.3803224755321</v>
+        <v>17.87428310803395</v>
       </c>
     </row>
     <row r="877">
@@ -7371,7 +7371,7 @@
         <v>875</v>
       </c>
       <c r="B877">
-        <v>14.11035630506033</v>
+        <v>14.70861967983075</v>
       </c>
     </row>
     <row r="878">
@@ -7379,7 +7379,7 @@
         <v>876</v>
       </c>
       <c r="B878">
-        <v>14.55254208396978</v>
+        <v>14.56119732156985</v>
       </c>
     </row>
     <row r="879">
@@ -7403,7 +7403,7 @@
         <v>879</v>
       </c>
       <c r="B881">
-        <v>10.78900252384516</v>
+        <v>11.0455365572774</v>
       </c>
     </row>
     <row r="882">
@@ -7827,7 +7827,7 @@
         <v>932</v>
       </c>
       <c r="B934">
-        <v>15.49414830618528</v>
+        <v>14.80921083333351</v>
       </c>
     </row>
     <row r="935">
@@ -7851,7 +7851,7 @@
         <v>935</v>
       </c>
       <c r="B937">
-        <v>14.1694078138738</v>
+        <v>13.41104083002249</v>
       </c>
     </row>
     <row r="938">
@@ -7867,7 +7867,7 @@
         <v>937</v>
       </c>
       <c r="B939">
-        <v>7.593248007981491</v>
+        <v>6.479186244217921</v>
       </c>
     </row>
     <row r="940">
@@ -7907,7 +7907,7 @@
         <v>942</v>
       </c>
       <c r="B944">
-        <v>11.03624346950976</v>
+        <v>9.316722992772174</v>
       </c>
     </row>
     <row r="945">
@@ -7915,7 +7915,7 @@
         <v>943</v>
       </c>
       <c r="B945">
-        <v>13.20512845698603</v>
+        <v>12.42437791206936</v>
       </c>
     </row>
     <row r="946">
@@ -8099,7 +8099,7 @@
         <v>966</v>
       </c>
       <c r="B968">
-        <v>8.920214792607071</v>
+        <v>11.85630293528173</v>
       </c>
     </row>
     <row r="969">
@@ -8107,7 +8107,7 @@
         <v>967</v>
       </c>
       <c r="B969">
-        <v>11.82964498135253</v>
+        <v>14.72806652491029</v>
       </c>
     </row>
     <row r="970">
@@ -8115,7 +8115,7 @@
         <v>968</v>
       </c>
       <c r="B970">
-        <v>14.12211206864431</v>
+        <v>16.65318338247413</v>
       </c>
     </row>
     <row r="971">
@@ -8123,7 +8123,7 @@
         <v>969</v>
       </c>
       <c r="B971">
-        <v>1.714410359024305</v>
+        <v>4.329742754778716</v>
       </c>
     </row>
     <row r="972">
@@ -8131,7 +8131,7 @@
         <v>970</v>
       </c>
       <c r="B972">
-        <v>9.985674461536117</v>
+        <v>12.06107822984307</v>
       </c>
     </row>
     <row r="973">
@@ -8139,7 +8139,7 @@
         <v>971</v>
       </c>
       <c r="B973">
-        <v>9.511204507116107</v>
+        <v>12.17875737154927</v>
       </c>
     </row>
     <row r="974">
@@ -8147,7 +8147,7 @@
         <v>972</v>
       </c>
       <c r="B974">
-        <v>9.812459017599531</v>
+        <v>12.53525088308245</v>
       </c>
     </row>
     <row r="975">
@@ -8155,7 +8155,7 @@
         <v>973</v>
       </c>
       <c r="B975">
-        <v>7.16712873994878</v>
+        <v>9.936982722872296</v>
       </c>
     </row>
     <row r="976">
@@ -8163,7 +8163,7 @@
         <v>974</v>
       </c>
       <c r="B976">
-        <v>10.8776215075781</v>
+        <v>13.10914744244024</v>
       </c>
     </row>
     <row r="977">
@@ -8171,7 +8171,7 @@
         <v>975</v>
       </c>
       <c r="B977">
-        <v>4.232436656350789</v>
+        <v>6.57723881833802</v>
       </c>
     </row>
     <row r="978">
@@ -8179,7 +8179,7 @@
         <v>976</v>
       </c>
       <c r="B978">
-        <v>14.51391367471693</v>
+        <v>17.35910146690644</v>
       </c>
     </row>
     <row r="979">
@@ -8187,7 +8187,7 @@
         <v>977</v>
       </c>
       <c r="B979">
-        <v>5.509956006905899</v>
+        <v>8.176936501283164</v>
       </c>
     </row>
     <row r="980">
@@ -8195,7 +8195,7 @@
         <v>978</v>
       </c>
       <c r="B980">
-        <v>6.602531664937675</v>
+        <v>8.420116806889435</v>
       </c>
     </row>
     <row r="981">
@@ -8203,7 +8203,7 @@
         <v>979</v>
       </c>
       <c r="B981">
-        <v>25.52254620683486</v>
+        <v>23.19789886850822</v>
       </c>
     </row>
     <row r="982">
@@ -8211,7 +8211,7 @@
         <v>980</v>
       </c>
       <c r="B982">
-        <v>22.09045143432118</v>
+        <v>19.56498261687737</v>
       </c>
     </row>
     <row r="983">
@@ -8219,7 +8219,7 @@
         <v>981</v>
       </c>
       <c r="B983">
-        <v>20.0478210117097</v>
+        <v>18.05641778626574</v>
       </c>
     </row>
     <row r="984">
@@ -8227,7 +8227,7 @@
         <v>982</v>
       </c>
       <c r="B984">
-        <v>18.12300782455958</v>
+        <v>15.44800993660738</v>
       </c>
     </row>
     <row r="985">
@@ -8235,7 +8235,7 @@
         <v>983</v>
       </c>
       <c r="B985">
-        <v>22.58286726743913</v>
+        <v>21.87330052677519</v>
       </c>
     </row>
     <row r="986">
@@ -8243,7 +8243,7 @@
         <v>984</v>
       </c>
       <c r="B986">
-        <v>17.50685840717249</v>
+        <v>15.33930621141995</v>
       </c>
     </row>
     <row r="987">
@@ -8251,7 +8251,7 @@
         <v>985</v>
       </c>
       <c r="B987">
-        <v>23.57932037443232</v>
+        <v>21.39926964535066</v>
       </c>
     </row>
     <row r="988">
@@ -8259,7 +8259,7 @@
         <v>986</v>
       </c>
       <c r="B988">
-        <v>28.66150841427597</v>
+        <v>26.62559967475715</v>
       </c>
     </row>
     <row r="989">
@@ -8347,7 +8347,7 @@
         <v>997</v>
       </c>
       <c r="B999">
-        <v>12.57761939936718</v>
+        <v>12.10556502925399</v>
       </c>
     </row>
     <row r="1000">
@@ -8363,7 +8363,7 @@
         <v>999</v>
       </c>
       <c r="B1001">
-        <v>14.59799581025459</v>
+        <v>12.82521446296451</v>
       </c>
     </row>
     <row r="1002">
@@ -8379,7 +8379,7 @@
         <v>1001</v>
       </c>
       <c r="B1003">
-        <v>14.60382992552079</v>
+        <v>11.92766163079851</v>
       </c>
     </row>
     <row r="1004">
@@ -8387,7 +8387,7 @@
         <v>1002</v>
       </c>
       <c r="B1004">
-        <v>12.83429868554952</v>
+        <v>10.5246677954652</v>
       </c>
     </row>
     <row r="1005">
@@ -8395,7 +8395,7 @@
         <v>1003</v>
       </c>
       <c r="B1005">
-        <v>11.30404102117589</v>
+        <v>8.823289604887609</v>
       </c>
     </row>
     <row r="1006">
@@ -8403,7 +8403,7 @@
         <v>1004</v>
       </c>
       <c r="B1006">
-        <v>11.7685686957084</v>
+        <v>8.845700007249018</v>
       </c>
     </row>
     <row r="1007">
@@ -8507,7 +8507,7 @@
         <v>1017</v>
       </c>
       <c r="B1019">
-        <v>22.8850024213061</v>
+        <v>21.77838752035956</v>
       </c>
     </row>
     <row r="1020">
@@ -8515,7 +8515,7 @@
         <v>1018</v>
       </c>
       <c r="B1020">
-        <v>20.3678326598375</v>
+        <v>18.87627066174108</v>
       </c>
     </row>
     <row r="1021">
@@ -8523,7 +8523,7 @@
         <v>1019</v>
       </c>
       <c r="B1021">
-        <v>23.56948507444276</v>
+        <v>21.86754100069239</v>
       </c>
     </row>
     <row r="1022">
@@ -8531,7 +8531,7 @@
         <v>1020</v>
       </c>
       <c r="B1022">
-        <v>8.727620073462889</v>
+        <v>5.895271467174473</v>
       </c>
     </row>
     <row r="1023">
@@ -8539,7 +8539,7 @@
         <v>1021</v>
       </c>
       <c r="B1023">
-        <v>6.7385465457903</v>
+        <v>4.926288307002339</v>
       </c>
     </row>
     <row r="1024">
@@ -8547,7 +8547,7 @@
         <v>1022</v>
       </c>
       <c r="B1024">
-        <v>10.43366744837717</v>
+        <v>8.315523484891372</v>
       </c>
     </row>
     <row r="1025">
@@ -8555,7 +8555,7 @@
         <v>1023</v>
       </c>
       <c r="B1025">
-        <v>8.118944230188216</v>
+        <v>5.349276700650416</v>
       </c>
     </row>
     <row r="1026">
@@ -8563,7 +8563,7 @@
         <v>1024</v>
       </c>
       <c r="B1026">
-        <v>9.508648129013466</v>
+        <v>7.111332213750659</v>
       </c>
     </row>
     <row r="1027">
@@ -8571,7 +8571,7 @@
         <v>1025</v>
       </c>
       <c r="B1027">
-        <v>21.64950372652624</v>
+        <v>22.22504355744513</v>
       </c>
     </row>
     <row r="1028">
@@ -8579,7 +8579,7 @@
         <v>1026</v>
       </c>
       <c r="B1028">
-        <v>7.100262537981658</v>
+        <v>7.624815221760368</v>
       </c>
     </row>
     <row r="1029">
@@ -8595,7 +8595,7 @@
         <v>1028</v>
       </c>
       <c r="B1030">
-        <v>21.19002101561528</v>
+        <v>22.66979779760182</v>
       </c>
     </row>
     <row r="1031">
@@ -8603,7 +8603,7 @@
         <v>1029</v>
       </c>
       <c r="B1031">
-        <v>10.89683881179044</v>
+        <v>12.14410868371082</v>
       </c>
     </row>
     <row r="1032">
@@ -8611,7 +8611,7 @@
         <v>1030</v>
       </c>
       <c r="B1032">
-        <v>2.699337278754647</v>
+        <v>3.829650916653252</v>
       </c>
     </row>
     <row r="1033">
@@ -8619,7 +8619,7 @@
         <v>1031</v>
       </c>
       <c r="B1033">
-        <v>17.74704956858763</v>
+        <v>19.69633273063405</v>
       </c>
     </row>
     <row r="1034">
@@ -8627,7 +8627,7 @@
         <v>1032</v>
       </c>
       <c r="B1034">
-        <v>16.55203774469037</v>
+        <v>17.98165975846372</v>
       </c>
     </row>
     <row r="1035">
@@ -8643,7 +8643,7 @@
         <v>1034</v>
       </c>
       <c r="B1036">
-        <v>12.10016086527797</v>
+        <v>13.81844086345078</v>
       </c>
     </row>
     <row r="1037">
@@ -8659,7 +8659,7 @@
         <v>1036</v>
       </c>
       <c r="B1038">
-        <v>14.41183207715983</v>
+        <v>16.72578789112604</v>
       </c>
     </row>
     <row r="1039">
@@ -8667,7 +8667,7 @@
         <v>1037</v>
       </c>
       <c r="B1039">
-        <v>16.52803447182866</v>
+        <v>18.22407726798037</v>
       </c>
     </row>
     <row r="1040">
@@ -8675,7 +8675,7 @@
         <v>1038</v>
       </c>
       <c r="B1040">
-        <v>16.60646821359574</v>
+        <v>18.83164021078667</v>
       </c>
     </row>
     <row r="1041">
@@ -8683,7 +8683,7 @@
         <v>1039</v>
       </c>
       <c r="B1041">
-        <v>20.16734568436619</v>
+        <v>20.15032488589116</v>
       </c>
     </row>
     <row r="1042">
@@ -8691,7 +8691,7 @@
         <v>1040</v>
       </c>
       <c r="B1042">
-        <v>15.77590722418053</v>
+        <v>16.95529327165244</v>
       </c>
     </row>
     <row r="1043">
@@ -8699,7 +8699,7 @@
         <v>1041</v>
       </c>
       <c r="B1043">
-        <v>26.00889933028632</v>
+        <v>25.76042506694605</v>
       </c>
     </row>
     <row r="1044">
@@ -8707,7 +8707,7 @@
         <v>1042</v>
       </c>
       <c r="B1044">
-        <v>18.88729517883474</v>
+        <v>19.89665323387234</v>
       </c>
     </row>
     <row r="1045">
@@ -8715,7 +8715,7 @@
         <v>1043</v>
       </c>
       <c r="B1045">
-        <v>7.091951068546098</v>
+        <v>9.014944674336999</v>
       </c>
     </row>
     <row r="1046">
@@ -8755,7 +8755,7 @@
         <v>1048</v>
       </c>
       <c r="B1050">
-        <v>17.34808611312392</v>
+        <v>17.8817238953763</v>
       </c>
     </row>
     <row r="1051">
@@ -9147,7 +9147,7 @@
         <v>1097</v>
       </c>
       <c r="B1099">
-        <v>13.30534833739332</v>
+        <v>16.22498622328425</v>
       </c>
     </row>
     <row r="1100">
@@ -9155,7 +9155,7 @@
         <v>1098</v>
       </c>
       <c r="B1100">
-        <v>16.59293432232049</v>
+        <v>18.16659459177931</v>
       </c>
     </row>
     <row r="1101">
@@ -9171,7 +9171,7 @@
         <v>1100</v>
       </c>
       <c r="B1102">
-        <v>12.91066863426261</v>
+        <v>15.65848541488306</v>
       </c>
     </row>
     <row r="1103">
@@ -9187,7 +9187,7 @@
         <v>1102</v>
       </c>
       <c r="B1104">
-        <v>16.33895280646302</v>
+        <v>19.16414331284514</v>
       </c>
     </row>
     <row r="1105">
@@ -9283,7 +9283,7 @@
         <v>1114</v>
       </c>
       <c r="B1116">
-        <v>21.58432581591429</v>
+        <v>23.250410214744</v>
       </c>
     </row>
     <row r="1117">
@@ -9315,7 +9315,7 @@
         <v>1118</v>
       </c>
       <c r="B1120">
-        <v>24.45335495349909</v>
+        <v>26.29896998594824</v>
       </c>
     </row>
     <row r="1121">
@@ -9331,7 +9331,7 @@
         <v>1120</v>
       </c>
       <c r="B1122">
-        <v>25.10865721582872</v>
+        <v>25.26335813791615</v>
       </c>
     </row>
     <row r="1123">
@@ -10395,7 +10395,7 @@
         <v>1253</v>
       </c>
       <c r="B1255">
-        <v>21.85403202765432</v>
+        <v>5.115910099815904</v>
       </c>
     </row>
     <row r="1256">
@@ -10403,7 +10403,7 @@
         <v>1254</v>
       </c>
       <c r="B1256">
-        <v>14.8541410947812</v>
+        <v>7.165155545677488</v>
       </c>
     </row>
     <row r="1257">
@@ -10411,7 +10411,7 @@
         <v>1255</v>
       </c>
       <c r="B1257">
-        <v>24.64220105478854</v>
+        <v>10.54637193708227</v>
       </c>
     </row>
     <row r="1258">
@@ -10419,7 +10419,7 @@
         <v>1256</v>
       </c>
       <c r="B1258">
-        <v>16.69553936735947</v>
+        <v>10.53803402039088</v>
       </c>
     </row>
     <row r="1259">
@@ -10427,7 +10427,7 @@
         <v>1257</v>
       </c>
       <c r="B1259">
-        <v>29.24852277694693</v>
+        <v>17.03890360230016</v>
       </c>
     </row>
     <row r="1260">
@@ -10435,7 +10435,7 @@
         <v>1258</v>
       </c>
       <c r="B1260">
-        <v>22.10770944611866</v>
+        <v>0.9783216269069993</v>
       </c>
     </row>
     <row r="1261">
@@ -10443,7 +10443,7 @@
         <v>1259</v>
       </c>
       <c r="B1261">
-        <v>20.40236004843402</v>
+        <v>9.622078735015201</v>
       </c>
     </row>
     <row r="1262">
@@ -10451,7 +10451,7 @@
         <v>1260</v>
       </c>
       <c r="B1262">
-        <v>30.60848773523942</v>
+        <v>11.65433004677049</v>
       </c>
     </row>
     <row r="1263">
@@ -10515,7 +10515,7 @@
         <v>1268</v>
       </c>
       <c r="B1270">
-        <v>45.8417117088315</v>
+        <v>33.89870420193641</v>
       </c>
     </row>
     <row r="1271">
@@ -10523,7 +10523,7 @@
         <v>1269</v>
       </c>
       <c r="B1271">
-        <v>37.73264472865329</v>
+        <v>23.85427479494686</v>
       </c>
     </row>
     <row r="1272">
@@ -10571,7 +10571,7 @@
         <v>1275</v>
       </c>
       <c r="B1277">
-        <v>41.05195009915524</v>
+        <v>36.54232466357547</v>
       </c>
     </row>
     <row r="1278">
@@ -10587,7 +10587,7 @@
         <v>1277</v>
       </c>
       <c r="B1279">
-        <v>44.75554580298125</v>
+        <v>27.18567404706327</v>
       </c>
     </row>
     <row r="1280">
@@ -10595,7 +10595,7 @@
         <v>1278</v>
       </c>
       <c r="B1280">
-        <v>38.37951012567792</v>
+        <v>19.63945069558143</v>
       </c>
     </row>
     <row r="1281">
@@ -10827,7 +10827,7 @@
         <v>1307</v>
       </c>
       <c r="B1309">
-        <v>28.35368382507527</v>
+        <v>7.112610490713061</v>
       </c>
     </row>
     <row r="1310">
@@ -10835,7 +10835,7 @@
         <v>1308</v>
       </c>
       <c r="B1310">
-        <v>27.06831850043861</v>
+        <v>12.37646107640634</v>
       </c>
     </row>
     <row r="1311">
@@ -10843,7 +10843,7 @@
         <v>1309</v>
       </c>
       <c r="B1311">
-        <v>31.96690754235217</v>
+        <v>19.73037499843991</v>
       </c>
     </row>
     <row r="1312">
@@ -10851,7 +10851,7 @@
         <v>1310</v>
       </c>
       <c r="B1312">
-        <v>21.68994269865124</v>
+        <v>14.96088807304816</v>
       </c>
     </row>
     <row r="1313">
@@ -10859,7 +10859,7 @@
         <v>1311</v>
       </c>
       <c r="B1313">
-        <v>26.94576079272844</v>
+        <v>15.88561743178249</v>
       </c>
     </row>
     <row r="1314">
@@ -10867,7 +10867,7 @@
         <v>1312</v>
       </c>
       <c r="B1314">
-        <v>30.73568146817878</v>
+        <v>10.69782096126851</v>
       </c>
     </row>
     <row r="1315">
@@ -10875,7 +10875,7 @@
         <v>1313</v>
       </c>
       <c r="B1315">
-        <v>20.33995777529206</v>
+        <v>17.00158203876426</v>
       </c>
     </row>
     <row r="1316">
@@ -10883,7 +10883,7 @@
         <v>1314</v>
       </c>
       <c r="B1316">
-        <v>27.82747714846036</v>
+        <v>18.89749147688468</v>
       </c>
     </row>
     <row r="1317">
@@ -10891,7 +10891,7 @@
         <v>1315</v>
       </c>
       <c r="B1317">
-        <v>23.58996290958255</v>
+        <v>14.07454650518082</v>
       </c>
     </row>
     <row r="1318">
@@ -11659,7 +11659,7 @@
         <v>1411</v>
       </c>
       <c r="B1413">
-        <v>21.69248433403215</v>
+        <v>18.34637498202288</v>
       </c>
     </row>
     <row r="1414">
@@ -11667,7 +11667,7 @@
         <v>1412</v>
       </c>
       <c r="B1414">
-        <v>26.26993740130826</v>
+        <v>23.5575121438225</v>
       </c>
     </row>
     <row r="1415">
@@ -11755,7 +11755,7 @@
         <v>1423</v>
       </c>
       <c r="B1425">
-        <v>23.48893072221871</v>
+        <v>18.54411854767321</v>
       </c>
     </row>
     <row r="1426">
@@ -12739,7 +12739,7 @@
         <v>1546</v>
       </c>
       <c r="B1548">
-        <v>27.73347318101185</v>
+        <v>20.79620857827781</v>
       </c>
     </row>
     <row r="1549">
@@ -12795,7 +12795,7 @@
         <v>1553</v>
       </c>
       <c r="B1555">
-        <v>30.98004413067966</v>
+        <v>29.94759290854302</v>
       </c>
     </row>
     <row r="1556">
@@ -12867,7 +12867,7 @@
         <v>1562</v>
       </c>
       <c r="B1564">
-        <v>38.7541348958684</v>
+        <v>31.21120582775341</v>
       </c>
     </row>
     <row r="1565">
@@ -12955,7 +12955,7 @@
         <v>1573</v>
       </c>
       <c r="B1575">
-        <v>5.171387257630506</v>
+        <v>3.754579480593483</v>
       </c>
     </row>
     <row r="1576">
@@ -13507,7 +13507,7 @@
         <v>1642</v>
       </c>
       <c r="B1644">
-        <v>4.963108320108936</v>
+        <v>2.028806557049571</v>
       </c>
     </row>
     <row r="1645">
@@ -13515,7 +13515,7 @@
         <v>1643</v>
       </c>
       <c r="B1645">
-        <v>2.594152426327075</v>
+        <v>0.833576887307609</v>
       </c>
     </row>
     <row r="1646">
@@ -13579,7 +13579,7 @@
         <v>1651</v>
       </c>
       <c r="B1653">
-        <v>28.45283509252831</v>
+        <v>26.43306470539659</v>
       </c>
     </row>
     <row r="1654">
@@ -13771,7 +13771,7 @@
         <v>1675</v>
       </c>
       <c r="B1677">
-        <v>15.34848158145213</v>
+        <v>7.314157409559792</v>
       </c>
     </row>
     <row r="1678">
@@ -13779,7 +13779,7 @@
         <v>1676</v>
       </c>
       <c r="B1678">
-        <v>25.23175643930555</v>
+        <v>7.244562685322004</v>
       </c>
     </row>
     <row r="1679">
@@ -13859,7 +13859,7 @@
         <v>1686</v>
       </c>
       <c r="B1688">
-        <v>19.21885102017499</v>
+        <v>16.98545211061418</v>
       </c>
     </row>
     <row r="1689">
@@ -13867,7 +13867,7 @@
         <v>1687</v>
       </c>
       <c r="B1689">
-        <v>16.82963245067203</v>
+        <v>15.62023236319789</v>
       </c>
     </row>
     <row r="1690">
@@ -13875,7 +13875,7 @@
         <v>1688</v>
       </c>
       <c r="B1690">
-        <v>9.188856624135081</v>
+        <v>8.213200592680051</v>
       </c>
     </row>
     <row r="1691">
@@ -13883,7 +13883,7 @@
         <v>1689</v>
       </c>
       <c r="B1691">
-        <v>14.02844543013261</v>
+        <v>12.38057977901964</v>
       </c>
     </row>
     <row r="1692">
@@ -13891,7 +13891,7 @@
         <v>1690</v>
       </c>
       <c r="B1692">
-        <v>16.82875973704438</v>
+        <v>17.2757676515808</v>
       </c>
     </row>
     <row r="1693">
@@ -13899,7 +13899,7 @@
         <v>1691</v>
       </c>
       <c r="B1693">
-        <v>15.40550577448183</v>
+        <v>13.32526951047298</v>
       </c>
     </row>
     <row r="1694">
@@ -13907,7 +13907,7 @@
         <v>1692</v>
       </c>
       <c r="B1694">
-        <v>19.28709925683625</v>
+        <v>18.65574960613958</v>
       </c>
     </row>
     <row r="1695">
@@ -13915,7 +13915,7 @@
         <v>1693</v>
       </c>
       <c r="B1695">
-        <v>12.02524259887938</v>
+        <v>10.51959486270761</v>
       </c>
     </row>
     <row r="1696">
@@ -13923,7 +13923,7 @@
         <v>1694</v>
       </c>
       <c r="B1696">
-        <v>11.75283238724364</v>
+        <v>12.01440772142921</v>
       </c>
     </row>
     <row r="1697">

--- a/Data/distance_to_nodes.xlsx
+++ b/Data/distance_to_nodes.xlsx
@@ -7099,7 +7099,7 @@
         <v>841</v>
       </c>
       <c r="B843">
-        <v>21.42181156028578</v>
+        <v>19.65390851242243</v>
       </c>
     </row>
     <row r="844">
@@ -7107,7 +7107,7 @@
         <v>842</v>
       </c>
       <c r="B844">
-        <v>22.49522263623879</v>
+        <v>21.38233355225105</v>
       </c>
     </row>
     <row r="845">
@@ -7115,7 +7115,7 @@
         <v>843</v>
       </c>
       <c r="B845">
-        <v>16.19161085190039</v>
+        <v>13.8605616975647</v>
       </c>
     </row>
     <row r="846">
@@ -7123,7 +7123,7 @@
         <v>844</v>
       </c>
       <c r="B846">
-        <v>20.9797932727014</v>
+        <v>18.69497252898393</v>
       </c>
     </row>
     <row r="847">
@@ -7131,7 +7131,7 @@
         <v>845</v>
       </c>
       <c r="B847">
-        <v>16.72536110107141</v>
+        <v>14.80905044784205</v>
       </c>
     </row>
     <row r="848">
@@ -7139,7 +7139,7 @@
         <v>846</v>
       </c>
       <c r="B848">
-        <v>19.50172462641531</v>
+        <v>18.39870558878141</v>
       </c>
     </row>
     <row r="849">
@@ -7155,7 +7155,7 @@
         <v>848</v>
       </c>
       <c r="B850">
-        <v>24.16635132296783</v>
+        <v>21.9705101648932</v>
       </c>
     </row>
     <row r="851">
@@ -7163,7 +7163,7 @@
         <v>849</v>
       </c>
       <c r="B851">
-        <v>19.49520767934272</v>
+        <v>16.90481363442589</v>
       </c>
     </row>
     <row r="852">
@@ -7171,7 +7171,7 @@
         <v>850</v>
       </c>
       <c r="B852">
-        <v>23.65685581179383</v>
+        <v>21.68222116567546</v>
       </c>
     </row>
     <row r="853">
@@ -7187,7 +7187,7 @@
         <v>852</v>
       </c>
       <c r="B854">
-        <v>16.62252273937216</v>
+        <v>15.24053375330743</v>
       </c>
     </row>
     <row r="855">
@@ -7299,7 +7299,7 @@
         <v>866</v>
       </c>
       <c r="B868">
-        <v>6.801876198379063</v>
+        <v>6.306982972332919</v>
       </c>
     </row>
     <row r="869">
@@ -7307,7 +7307,7 @@
         <v>867</v>
       </c>
       <c r="B869">
-        <v>8.900894857005918</v>
+        <v>8.93959382185113</v>
       </c>
     </row>
     <row r="870">
@@ -7323,7 +7323,7 @@
         <v>869</v>
       </c>
       <c r="B871">
-        <v>11.96872854148653</v>
+        <v>10.91660469586549</v>
       </c>
     </row>
     <row r="872">
@@ -7347,7 +7347,7 @@
         <v>872</v>
       </c>
       <c r="B874">
-        <v>18.27377477470923</v>
+        <v>18.6967397880025</v>
       </c>
     </row>
     <row r="875">
@@ -7363,7 +7363,7 @@
         <v>874</v>
       </c>
       <c r="B876">
-        <v>17.87428310803395</v>
+        <v>17.3803224755321</v>
       </c>
     </row>
     <row r="877">
@@ -7371,7 +7371,7 @@
         <v>875</v>
       </c>
       <c r="B877">
-        <v>14.70861967983075</v>
+        <v>14.11035630506033</v>
       </c>
     </row>
     <row r="878">
@@ -7379,7 +7379,7 @@
         <v>876</v>
       </c>
       <c r="B878">
-        <v>14.56119732156985</v>
+        <v>14.55254208396978</v>
       </c>
     </row>
     <row r="879">
@@ -7403,7 +7403,7 @@
         <v>879</v>
       </c>
       <c r="B881">
-        <v>11.0455365572774</v>
+        <v>10.78900252384516</v>
       </c>
     </row>
     <row r="882">
@@ -7827,7 +7827,7 @@
         <v>932</v>
       </c>
       <c r="B934">
-        <v>14.80921083333351</v>
+        <v>15.49414830618528</v>
       </c>
     </row>
     <row r="935">
@@ -7851,7 +7851,7 @@
         <v>935</v>
       </c>
       <c r="B937">
-        <v>13.41104083002249</v>
+        <v>14.1694078138738</v>
       </c>
     </row>
     <row r="938">
@@ -7867,7 +7867,7 @@
         <v>937</v>
       </c>
       <c r="B939">
-        <v>6.479186244217921</v>
+        <v>7.593248007981491</v>
       </c>
     </row>
     <row r="940">
@@ -7907,7 +7907,7 @@
         <v>942</v>
       </c>
       <c r="B944">
-        <v>9.316722992772174</v>
+        <v>11.03624346950976</v>
       </c>
     </row>
     <row r="945">
@@ -7915,7 +7915,7 @@
         <v>943</v>
       </c>
       <c r="B945">
-        <v>12.42437791206936</v>
+        <v>13.20512845698603</v>
       </c>
     </row>
     <row r="946">
@@ -8099,7 +8099,7 @@
         <v>966</v>
       </c>
       <c r="B968">
-        <v>11.85630293528173</v>
+        <v>8.920214792607071</v>
       </c>
     </row>
     <row r="969">
@@ -8107,7 +8107,7 @@
         <v>967</v>
       </c>
       <c r="B969">
-        <v>14.72806652491029</v>
+        <v>11.82964498135253</v>
       </c>
     </row>
     <row r="970">
@@ -8115,7 +8115,7 @@
         <v>968</v>
       </c>
       <c r="B970">
-        <v>16.65318338247413</v>
+        <v>14.12211206864431</v>
       </c>
     </row>
     <row r="971">
@@ -8123,7 +8123,7 @@
         <v>969</v>
       </c>
       <c r="B971">
-        <v>4.329742754778716</v>
+        <v>1.714410359024305</v>
       </c>
     </row>
     <row r="972">
@@ -8131,7 +8131,7 @@
         <v>970</v>
       </c>
       <c r="B972">
-        <v>12.06107822984307</v>
+        <v>9.985674461536117</v>
       </c>
     </row>
     <row r="973">
@@ -8139,7 +8139,7 @@
         <v>971</v>
       </c>
       <c r="B973">
-        <v>12.17875737154927</v>
+        <v>9.511204507116107</v>
       </c>
     </row>
     <row r="974">
@@ -8147,7 +8147,7 @@
         <v>972</v>
       </c>
       <c r="B974">
-        <v>12.53525088308245</v>
+        <v>9.812459017599531</v>
       </c>
     </row>
     <row r="975">
@@ -8155,7 +8155,7 @@
         <v>973</v>
       </c>
       <c r="B975">
-        <v>9.936982722872296</v>
+        <v>7.16712873994878</v>
       </c>
     </row>
     <row r="976">
@@ -8163,7 +8163,7 @@
         <v>974</v>
       </c>
       <c r="B976">
-        <v>13.10914744244024</v>
+        <v>10.8776215075781</v>
       </c>
     </row>
     <row r="977">
@@ -8171,7 +8171,7 @@
         <v>975</v>
       </c>
       <c r="B977">
-        <v>6.57723881833802</v>
+        <v>4.232436656350789</v>
       </c>
     </row>
     <row r="978">
@@ -8179,7 +8179,7 @@
         <v>976</v>
       </c>
       <c r="B978">
-        <v>17.35910146690644</v>
+        <v>14.51391367471693</v>
       </c>
     </row>
     <row r="979">
@@ -8187,7 +8187,7 @@
         <v>977</v>
       </c>
       <c r="B979">
-        <v>8.176936501283164</v>
+        <v>5.509956006905899</v>
       </c>
     </row>
     <row r="980">
@@ -8195,7 +8195,7 @@
         <v>978</v>
       </c>
       <c r="B980">
-        <v>8.420116806889435</v>
+        <v>6.602531664937675</v>
       </c>
     </row>
     <row r="981">
@@ -8203,7 +8203,7 @@
         <v>979</v>
       </c>
       <c r="B981">
-        <v>23.19789886850822</v>
+        <v>25.52254620683486</v>
       </c>
     </row>
     <row r="982">
@@ -8211,7 +8211,7 @@
         <v>980</v>
       </c>
       <c r="B982">
-        <v>19.56498261687737</v>
+        <v>22.09045143432118</v>
       </c>
     </row>
     <row r="983">
@@ -8219,7 +8219,7 @@
         <v>981</v>
       </c>
       <c r="B983">
-        <v>18.05641778626574</v>
+        <v>20.0478210117097</v>
       </c>
     </row>
     <row r="984">
@@ -8227,7 +8227,7 @@
         <v>982</v>
       </c>
       <c r="B984">
-        <v>15.44800993660738</v>
+        <v>18.12300782455958</v>
       </c>
     </row>
     <row r="985">
@@ -8235,7 +8235,7 @@
         <v>983</v>
       </c>
       <c r="B985">
-        <v>21.87330052677519</v>
+        <v>22.58286726743913</v>
       </c>
     </row>
     <row r="986">
@@ -8243,7 +8243,7 @@
         <v>984</v>
       </c>
       <c r="B986">
-        <v>15.33930621141995</v>
+        <v>17.50685840717249</v>
       </c>
     </row>
     <row r="987">
@@ -8251,7 +8251,7 @@
         <v>985</v>
       </c>
       <c r="B987">
-        <v>21.39926964535066</v>
+        <v>23.57932037443232</v>
       </c>
     </row>
     <row r="988">
@@ -8259,7 +8259,7 @@
         <v>986</v>
       </c>
       <c r="B988">
-        <v>26.62559967475715</v>
+        <v>28.66150841427597</v>
       </c>
     </row>
     <row r="989">
@@ -8347,7 +8347,7 @@
         <v>997</v>
       </c>
       <c r="B999">
-        <v>12.10556502925399</v>
+        <v>12.57761939936718</v>
       </c>
     </row>
     <row r="1000">
@@ -8363,7 +8363,7 @@
         <v>999</v>
       </c>
       <c r="B1001">
-        <v>12.82521446296451</v>
+        <v>14.59799581025459</v>
       </c>
     </row>
     <row r="1002">
@@ -8379,7 +8379,7 @@
         <v>1001</v>
       </c>
       <c r="B1003">
-        <v>11.92766163079851</v>
+        <v>14.60382992552079</v>
       </c>
     </row>
     <row r="1004">
@@ -8387,7 +8387,7 @@
         <v>1002</v>
       </c>
       <c r="B1004">
-        <v>10.5246677954652</v>
+        <v>12.83429868554952</v>
       </c>
     </row>
     <row r="1005">
@@ -8395,7 +8395,7 @@
         <v>1003</v>
       </c>
       <c r="B1005">
-        <v>8.823289604887609</v>
+        <v>11.30404102117589</v>
       </c>
     </row>
     <row r="1006">
@@ -8403,7 +8403,7 @@
         <v>1004</v>
       </c>
       <c r="B1006">
-        <v>8.845700007249018</v>
+        <v>11.7685686957084</v>
       </c>
     </row>
     <row r="1007">
@@ -8507,7 +8507,7 @@
         <v>1017</v>
       </c>
       <c r="B1019">
-        <v>21.77838752035956</v>
+        <v>22.8850024213061</v>
       </c>
     </row>
     <row r="1020">
@@ -8515,7 +8515,7 @@
         <v>1018</v>
       </c>
       <c r="B1020">
-        <v>18.87627066174108</v>
+        <v>20.3678326598375</v>
       </c>
     </row>
     <row r="1021">
@@ -8523,7 +8523,7 @@
         <v>1019</v>
       </c>
       <c r="B1021">
-        <v>21.86754100069239</v>
+        <v>23.56948507444276</v>
       </c>
     </row>
     <row r="1022">
@@ -8531,7 +8531,7 @@
         <v>1020</v>
       </c>
       <c r="B1022">
-        <v>5.895271467174473</v>
+        <v>8.727620073462889</v>
       </c>
     </row>
     <row r="1023">
@@ -8539,7 +8539,7 @@
         <v>1021</v>
       </c>
       <c r="B1023">
-        <v>4.926288307002339</v>
+        <v>6.7385465457903</v>
       </c>
     </row>
     <row r="1024">
@@ -8547,7 +8547,7 @@
         <v>1022</v>
       </c>
       <c r="B1024">
-        <v>8.315523484891372</v>
+        <v>10.43366744837717</v>
       </c>
     </row>
     <row r="1025">
@@ -8555,7 +8555,7 @@
         <v>1023</v>
       </c>
       <c r="B1025">
-        <v>5.349276700650416</v>
+        <v>8.118944230188216</v>
       </c>
     </row>
     <row r="1026">
@@ -8563,7 +8563,7 @@
         <v>1024</v>
       </c>
       <c r="B1026">
-        <v>7.111332213750659</v>
+        <v>9.508648129013466</v>
       </c>
     </row>
     <row r="1027">
@@ -8571,7 +8571,7 @@
         <v>1025</v>
       </c>
       <c r="B1027">
-        <v>22.22504355744513</v>
+        <v>21.64950372652624</v>
       </c>
     </row>
     <row r="1028">
@@ -8579,7 +8579,7 @@
         <v>1026</v>
       </c>
       <c r="B1028">
-        <v>7.624815221760368</v>
+        <v>7.100262537981658</v>
       </c>
     </row>
     <row r="1029">
@@ -8595,7 +8595,7 @@
         <v>1028</v>
       </c>
       <c r="B1030">
-        <v>22.66979779760182</v>
+        <v>21.19002101561528</v>
       </c>
     </row>
     <row r="1031">
@@ -8603,7 +8603,7 @@
         <v>1029</v>
       </c>
       <c r="B1031">
-        <v>12.14410868371082</v>
+        <v>10.89683881179044</v>
       </c>
     </row>
     <row r="1032">
@@ -8611,7 +8611,7 @@
         <v>1030</v>
       </c>
       <c r="B1032">
-        <v>3.829650916653252</v>
+        <v>2.699337278754647</v>
       </c>
     </row>
     <row r="1033">
@@ -8619,7 +8619,7 @@
         <v>1031</v>
       </c>
       <c r="B1033">
-        <v>19.69633273063405</v>
+        <v>17.74704956858763</v>
       </c>
     </row>
     <row r="1034">
@@ -8627,7 +8627,7 @@
         <v>1032</v>
       </c>
       <c r="B1034">
-        <v>17.98165975846372</v>
+        <v>16.55203774469037</v>
       </c>
     </row>
     <row r="1035">
@@ -8643,7 +8643,7 @@
         <v>1034</v>
       </c>
       <c r="B1036">
-        <v>13.81844086345078</v>
+        <v>12.10016086527797</v>
       </c>
     </row>
     <row r="1037">
@@ -8659,7 +8659,7 @@
         <v>1036</v>
       </c>
       <c r="B1038">
-        <v>16.72578789112604</v>
+        <v>14.41183207715983</v>
       </c>
     </row>
     <row r="1039">
@@ -8667,7 +8667,7 @@
         <v>1037</v>
       </c>
       <c r="B1039">
-        <v>18.22407726798037</v>
+        <v>16.52803447182866</v>
       </c>
     </row>
     <row r="1040">
@@ -8675,7 +8675,7 @@
         <v>1038</v>
       </c>
       <c r="B1040">
-        <v>18.83164021078667</v>
+        <v>16.60646821359574</v>
       </c>
     </row>
     <row r="1041">
@@ -8683,7 +8683,7 @@
         <v>1039</v>
       </c>
       <c r="B1041">
-        <v>20.15032488589116</v>
+        <v>20.16734568436619</v>
       </c>
     </row>
     <row r="1042">
@@ -8691,7 +8691,7 @@
         <v>1040</v>
       </c>
       <c r="B1042">
-        <v>16.95529327165244</v>
+        <v>15.77590722418053</v>
       </c>
     </row>
     <row r="1043">
@@ -8699,7 +8699,7 @@
         <v>1041</v>
       </c>
       <c r="B1043">
-        <v>25.76042506694605</v>
+        <v>26.00889933028632</v>
       </c>
     </row>
     <row r="1044">
@@ -8707,7 +8707,7 @@
         <v>1042</v>
       </c>
       <c r="B1044">
-        <v>19.89665323387234</v>
+        <v>18.88729517883474</v>
       </c>
     </row>
     <row r="1045">
@@ -8715,7 +8715,7 @@
         <v>1043</v>
       </c>
       <c r="B1045">
-        <v>9.014944674336999</v>
+        <v>7.091951068546098</v>
       </c>
     </row>
     <row r="1046">
@@ -8755,7 +8755,7 @@
         <v>1048</v>
       </c>
       <c r="B1050">
-        <v>17.8817238953763</v>
+        <v>17.34808611312392</v>
       </c>
     </row>
     <row r="1051">
@@ -9147,7 +9147,7 @@
         <v>1097</v>
       </c>
       <c r="B1099">
-        <v>16.22498622328425</v>
+        <v>13.30534833739332</v>
       </c>
     </row>
     <row r="1100">
@@ -9155,7 +9155,7 @@
         <v>1098</v>
       </c>
       <c r="B1100">
-        <v>18.16659459177931</v>
+        <v>16.59293432232049</v>
       </c>
     </row>
     <row r="1101">
@@ -9171,7 +9171,7 @@
         <v>1100</v>
       </c>
       <c r="B1102">
-        <v>15.65848541488306</v>
+        <v>12.91066863426261</v>
       </c>
     </row>
     <row r="1103">
@@ -9187,7 +9187,7 @@
         <v>1102</v>
       </c>
       <c r="B1104">
-        <v>19.16414331284514</v>
+        <v>16.33895280646302</v>
       </c>
     </row>
     <row r="1105">
@@ -9283,7 +9283,7 @@
         <v>1114</v>
       </c>
       <c r="B1116">
-        <v>23.250410214744</v>
+        <v>21.58432581591429</v>
       </c>
     </row>
     <row r="1117">
@@ -9315,7 +9315,7 @@
         <v>1118</v>
       </c>
       <c r="B1120">
-        <v>26.29896998594824</v>
+        <v>24.45335495349909</v>
       </c>
     </row>
     <row r="1121">
@@ -9331,7 +9331,7 @@
         <v>1120</v>
       </c>
       <c r="B1122">
-        <v>25.26335813791615</v>
+        <v>25.10865721582872</v>
       </c>
     </row>
     <row r="1123">
@@ -12955,7 +12955,7 @@
         <v>1573</v>
       </c>
       <c r="B1575">
-        <v>3.754579480593483</v>
+        <v>5.171387257630506</v>
       </c>
     </row>
     <row r="1576">
@@ -13507,7 +13507,7 @@
         <v>1642</v>
       </c>
       <c r="B1644">
-        <v>2.028806557049571</v>
+        <v>4.963108320108936</v>
       </c>
     </row>
     <row r="1645">
@@ -13515,7 +13515,7 @@
         <v>1643</v>
       </c>
       <c r="B1645">
-        <v>0.833576887307609</v>
+        <v>2.594152426327075</v>
       </c>
     </row>
     <row r="1646">
@@ -13579,7 +13579,7 @@
         <v>1651</v>
       </c>
       <c r="B1653">
-        <v>26.43306470539659</v>
+        <v>28.45283509252831</v>
       </c>
     </row>
     <row r="1654">
@@ -13859,7 +13859,7 @@
         <v>1686</v>
       </c>
       <c r="B1688">
-        <v>16.98545211061418</v>
+        <v>19.21885102017499</v>
       </c>
     </row>
     <row r="1689">
@@ -13867,7 +13867,7 @@
         <v>1687</v>
       </c>
       <c r="B1689">
-        <v>15.62023236319789</v>
+        <v>16.82963245067203</v>
       </c>
     </row>
     <row r="1690">
@@ -13875,7 +13875,7 @@
         <v>1688</v>
       </c>
       <c r="B1690">
-        <v>8.213200592680051</v>
+        <v>9.188856624135081</v>
       </c>
     </row>
     <row r="1691">
@@ -13883,7 +13883,7 @@
         <v>1689</v>
       </c>
       <c r="B1691">
-        <v>12.38057977901964</v>
+        <v>14.02844543013261</v>
       </c>
     </row>
     <row r="1692">
@@ -13891,7 +13891,7 @@
         <v>1690</v>
       </c>
       <c r="B1692">
-        <v>17.2757676515808</v>
+        <v>16.82875973704438</v>
       </c>
     </row>
     <row r="1693">
@@ -13899,7 +13899,7 @@
         <v>1691</v>
       </c>
       <c r="B1693">
-        <v>13.32526951047298</v>
+        <v>15.40550577448183</v>
       </c>
     </row>
     <row r="1694">
@@ -13907,7 +13907,7 @@
         <v>1692</v>
       </c>
       <c r="B1694">
-        <v>18.65574960613958</v>
+        <v>19.28709925683625</v>
       </c>
     </row>
     <row r="1695">
@@ -13915,7 +13915,7 @@
         <v>1693</v>
       </c>
       <c r="B1695">
-        <v>10.51959486270761</v>
+        <v>12.02524259887938</v>
       </c>
     </row>
     <row r="1696">
@@ -13923,7 +13923,7 @@
         <v>1694</v>
       </c>
       <c r="B1696">
-        <v>12.01440772142921</v>
+        <v>11.75283238724364</v>
       </c>
     </row>
     <row r="1697">

--- a/Data/distance_to_nodes.xlsx
+++ b/Data/distance_to_nodes.xlsx
@@ -10395,7 +10395,7 @@
         <v>1253</v>
       </c>
       <c r="B1255">
-        <v>5.115910099815904</v>
+        <v>21.85403202765432</v>
       </c>
     </row>
     <row r="1256">
@@ -10403,7 +10403,7 @@
         <v>1254</v>
       </c>
       <c r="B1256">
-        <v>7.165155545677488</v>
+        <v>14.8541410947812</v>
       </c>
     </row>
     <row r="1257">
@@ -10411,7 +10411,7 @@
         <v>1255</v>
       </c>
       <c r="B1257">
-        <v>10.54637193708227</v>
+        <v>24.64220105478854</v>
       </c>
     </row>
     <row r="1258">
@@ -10419,7 +10419,7 @@
         <v>1256</v>
       </c>
       <c r="B1258">
-        <v>10.53803402039088</v>
+        <v>16.69553936735947</v>
       </c>
     </row>
     <row r="1259">
@@ -10427,7 +10427,7 @@
         <v>1257</v>
       </c>
       <c r="B1259">
-        <v>17.03890360230016</v>
+        <v>29.24852277694693</v>
       </c>
     </row>
     <row r="1260">
@@ -10435,7 +10435,7 @@
         <v>1258</v>
       </c>
       <c r="B1260">
-        <v>0.9783216269069993</v>
+        <v>22.10770944611866</v>
       </c>
     </row>
     <row r="1261">
@@ -10443,7 +10443,7 @@
         <v>1259</v>
       </c>
       <c r="B1261">
-        <v>9.622078735015201</v>
+        <v>20.40236004843402</v>
       </c>
     </row>
     <row r="1262">
@@ -10451,7 +10451,7 @@
         <v>1260</v>
       </c>
       <c r="B1262">
-        <v>11.65433004677049</v>
+        <v>30.60848773523942</v>
       </c>
     </row>
     <row r="1263">
@@ -10515,7 +10515,7 @@
         <v>1268</v>
       </c>
       <c r="B1270">
-        <v>33.89870420193641</v>
+        <v>45.8417117088315</v>
       </c>
     </row>
     <row r="1271">
@@ -10523,7 +10523,7 @@
         <v>1269</v>
       </c>
       <c r="B1271">
-        <v>23.85427479494686</v>
+        <v>37.73264472865329</v>
       </c>
     </row>
     <row r="1272">
@@ -10571,7 +10571,7 @@
         <v>1275</v>
       </c>
       <c r="B1277">
-        <v>36.54232466357547</v>
+        <v>41.05195009915524</v>
       </c>
     </row>
     <row r="1278">
@@ -10587,7 +10587,7 @@
         <v>1277</v>
       </c>
       <c r="B1279">
-        <v>27.18567404706327</v>
+        <v>44.75554580298125</v>
       </c>
     </row>
     <row r="1280">
@@ -10595,7 +10595,7 @@
         <v>1278</v>
       </c>
       <c r="B1280">
-        <v>19.63945069558143</v>
+        <v>38.37951012567792</v>
       </c>
     </row>
     <row r="1281">
@@ -10827,7 +10827,7 @@
         <v>1307</v>
       </c>
       <c r="B1309">
-        <v>7.112610490713061</v>
+        <v>28.35368382507527</v>
       </c>
     </row>
     <row r="1310">
@@ -10835,7 +10835,7 @@
         <v>1308</v>
       </c>
       <c r="B1310">
-        <v>12.37646107640634</v>
+        <v>27.06831850043861</v>
       </c>
     </row>
     <row r="1311">
@@ -10843,7 +10843,7 @@
         <v>1309</v>
       </c>
       <c r="B1311">
-        <v>19.73037499843991</v>
+        <v>31.96690754235217</v>
       </c>
     </row>
     <row r="1312">
@@ -10851,7 +10851,7 @@
         <v>1310</v>
       </c>
       <c r="B1312">
-        <v>14.96088807304816</v>
+        <v>21.68994269865124</v>
       </c>
     </row>
     <row r="1313">
@@ -10859,7 +10859,7 @@
         <v>1311</v>
       </c>
       <c r="B1313">
-        <v>15.88561743178249</v>
+        <v>26.94576079272844</v>
       </c>
     </row>
     <row r="1314">
@@ -10867,7 +10867,7 @@
         <v>1312</v>
       </c>
       <c r="B1314">
-        <v>10.69782096126851</v>
+        <v>30.73568146817878</v>
       </c>
     </row>
     <row r="1315">
@@ -10875,7 +10875,7 @@
         <v>1313</v>
       </c>
       <c r="B1315">
-        <v>17.00158203876426</v>
+        <v>20.33995777529206</v>
       </c>
     </row>
     <row r="1316">
@@ -10883,7 +10883,7 @@
         <v>1314</v>
       </c>
       <c r="B1316">
-        <v>18.89749147688468</v>
+        <v>27.82747714846036</v>
       </c>
     </row>
     <row r="1317">
@@ -10891,7 +10891,7 @@
         <v>1315</v>
       </c>
       <c r="B1317">
-        <v>14.07454650518082</v>
+        <v>23.58996290958255</v>
       </c>
     </row>
     <row r="1318">
@@ -11659,7 +11659,7 @@
         <v>1411</v>
       </c>
       <c r="B1413">
-        <v>18.34637498202288</v>
+        <v>21.69248433403215</v>
       </c>
     </row>
     <row r="1414">
@@ -11667,7 +11667,7 @@
         <v>1412</v>
       </c>
       <c r="B1414">
-        <v>23.5575121438225</v>
+        <v>26.26993740130826</v>
       </c>
     </row>
     <row r="1415">
@@ -11755,7 +11755,7 @@
         <v>1423</v>
       </c>
       <c r="B1425">
-        <v>18.54411854767321</v>
+        <v>23.48893072221871</v>
       </c>
     </row>
     <row r="1426">
@@ -12739,7 +12739,7 @@
         <v>1546</v>
       </c>
       <c r="B1548">
-        <v>20.79620857827781</v>
+        <v>27.73347318101185</v>
       </c>
     </row>
     <row r="1549">
@@ -12795,7 +12795,7 @@
         <v>1553</v>
       </c>
       <c r="B1555">
-        <v>29.94759290854302</v>
+        <v>30.98004413067966</v>
       </c>
     </row>
     <row r="1556">
@@ -12867,7 +12867,7 @@
         <v>1562</v>
       </c>
       <c r="B1564">
-        <v>31.21120582775341</v>
+        <v>38.7541348958684</v>
       </c>
     </row>
     <row r="1565">
@@ -13771,7 +13771,7 @@
         <v>1675</v>
       </c>
       <c r="B1677">
-        <v>7.314157409559792</v>
+        <v>15.34848158145213</v>
       </c>
     </row>
     <row r="1678">
@@ -13779,7 +13779,7 @@
         <v>1676</v>
       </c>
       <c r="B1678">
-        <v>7.244562685322004</v>
+        <v>25.23175643930555</v>
       </c>
     </row>
     <row r="1679">
